--- a/22:23/PLteamsData22:23_with_tight_schedule.xlsx
+++ b/22:23/PLteamsData22:23_with_tight_schedule.xlsx
@@ -1089,7 +1089,7 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1121,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1185,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1249,7 +1249,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1281,7 +1281,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1313,7 +1313,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1409,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1537,7 +1537,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1633,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1665,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1697,7 +1697,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1729,7 +1729,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1793,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1825,7 +1825,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1953,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2145,7 +2145,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2209,7 +2209,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2344,7 +2344,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2536,7 +2536,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2568,7 +2568,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2696,7 +2696,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2728,7 +2728,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2760,7 +2760,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2792,7 +2792,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2888,7 +2888,7 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2952,7 +2952,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3016,7 +3016,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -3048,7 +3048,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -3080,7 +3080,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -3141,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -3205,7 +3205,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -3269,7 +3269,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -3397,7 +3397,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3596,7 +3596,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3628,7 +3628,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3692,7 +3692,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3788,7 +3788,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3820,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3852,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3916,7 +3916,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3948,7 +3948,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3980,7 +3980,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4012,7 +4012,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4140,7 +4140,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4172,7 +4172,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4236,7 +4236,7 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4268,7 +4268,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4332,7 +4332,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4364,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4428,7 +4428,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4460,7 +4460,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -4492,7 +4492,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -4524,7 +4524,7 @@
         <v>5</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -4652,7 +4652,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -4851,7 +4851,7 @@
         <v>7</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4883,7 +4883,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5043,7 +5043,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5075,7 +5075,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5139,7 +5139,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5171,7 +5171,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5267,7 +5267,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -5363,7 +5363,7 @@
         <v>5</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5427,7 +5427,7 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5619,7 +5619,7 @@
         <v>5</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5747,7 +5747,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -5779,7 +5779,7 @@
         <v>5</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -5907,7 +5907,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -6138,7 +6138,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6298,7 +6298,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6330,7 +6330,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6362,7 +6362,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6458,7 +6458,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6490,7 +6490,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6522,7 +6522,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6586,7 +6586,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6618,7 +6618,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6810,7 +6810,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6938,7 +6938,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7002,7 +7002,7 @@
         <v>6</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -7162,7 +7162,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -7361,7 +7361,7 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7393,7 +7393,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7617,7 +7617,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7713,7 +7713,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7777,7 +7777,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -8065,7 +8065,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8097,7 +8097,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -8129,7 +8129,7 @@
         <v>5</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -8222,7 +8222,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -8286,7 +8286,7 @@
         <v>5</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -8318,7 +8318,7 @@
         <v>5</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -8414,7 +8414,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -8613,7 +8613,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -8645,7 +8645,7 @@
         <v>7</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -8805,7 +8805,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -8837,7 +8837,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -8869,7 +8869,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -8901,7 +8901,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -8997,7 +8997,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -9125,7 +9125,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9253,7 +9253,7 @@
         <v>7</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9285,7 +9285,7 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -9317,7 +9317,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -9381,7 +9381,7 @@
         <v>6</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -9445,7 +9445,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -9509,7 +9509,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -9669,7 +9669,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -9733,7 +9733,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9900,7 +9900,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -10124,7 +10124,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -10156,7 +10156,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -10188,7 +10188,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -10220,7 +10220,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -10284,7 +10284,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -10316,7 +10316,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -10476,7 +10476,7 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -10604,7 +10604,7 @@
         <v>5</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -10636,7 +10636,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -10764,7 +10764,7 @@
         <v>6</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -10956,7 +10956,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -11155,7 +11155,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -11315,7 +11315,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -11379,7 +11379,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -11411,7 +11411,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -11443,7 +11443,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -11475,7 +11475,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -11635,7 +11635,7 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -11667,7 +11667,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -11699,7 +11699,7 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -11731,7 +11731,7 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -11827,7 +11827,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -11891,7 +11891,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -11955,7 +11955,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -11987,7 +11987,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -12019,7 +12019,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -12179,7 +12179,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -12243,7 +12243,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12442,7 +12442,7 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -12634,7 +12634,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -12666,7 +12666,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -12698,7 +12698,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -12762,7 +12762,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -12794,7 +12794,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -12826,7 +12826,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -12858,7 +12858,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -12922,7 +12922,7 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -12954,7 +12954,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -13082,7 +13082,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -13114,7 +13114,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -13146,7 +13146,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -13274,7 +13274,7 @@
         <v>6</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -13466,7 +13466,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -13633,7 +13633,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -13665,7 +13665,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -13825,7 +13825,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -13857,7 +13857,7 @@
         <v>5</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -13889,7 +13889,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -13953,7 +13953,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -13985,7 +13985,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -14177,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -14337,7 +14337,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -14369,7 +14369,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -14401,7 +14401,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -14465,7 +14465,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -14497,7 +14497,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -14529,7 +14529,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -14689,7 +14689,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -14920,7 +14920,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -15112,7 +15112,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15144,7 +15144,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15208,7 +15208,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15240,7 +15240,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -15272,7 +15272,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15336,7 +15336,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -15464,7 +15464,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -15496,7 +15496,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -15560,7 +15560,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -15592,7 +15592,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -15624,7 +15624,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -15656,7 +15656,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -15752,7 +15752,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -15784,7 +15784,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -15976,7 +15976,7 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -16175,7 +16175,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -16335,7 +16335,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -16367,7 +16367,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -16399,7 +16399,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -16431,7 +16431,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -16463,7 +16463,7 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -16495,7 +16495,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -16591,7 +16591,7 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -16655,7 +16655,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -16687,7 +16687,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -16719,7 +16719,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -16815,7 +16815,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -16847,7 +16847,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -16879,7 +16879,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -16975,7 +16975,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -17007,7 +17007,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -17199,7 +17199,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -17263,7 +17263,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -17398,7 +17398,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -17430,7 +17430,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -17590,7 +17590,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -17622,7 +17622,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -17654,7 +17654,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -17686,7 +17686,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -17718,7 +17718,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -17750,7 +17750,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -17782,7 +17782,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -17814,7 +17814,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -17942,7 +17942,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -18070,7 +18070,7 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -18102,7 +18102,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -18134,7 +18134,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -18230,7 +18230,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -18262,7 +18262,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -18294,7 +18294,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -18454,7 +18454,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -18653,7 +18653,7 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -18685,7 +18685,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -18749,7 +18749,7 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -18845,7 +18845,7 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -18877,7 +18877,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -18909,7 +18909,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -18941,7 +18941,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -19005,7 +19005,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -19197,7 +19197,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -19229,7 +19229,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -19325,7 +19325,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -19389,7 +19389,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -19485,7 +19485,7 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -19517,7 +19517,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -19549,7 +19549,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -19709,7 +19709,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -19908,7 +19908,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -19940,7 +19940,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20100,7 +20100,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20132,7 +20132,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -20164,7 +20164,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -20196,7 +20196,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -20260,7 +20260,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -20420,7 +20420,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -20516,7 +20516,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -20580,7 +20580,7 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -20772,7 +20772,7 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -20836,7 +20836,7 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -20900,7 +20900,7 @@
         <v>5</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -21028,7 +21028,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21419,7 +21419,7 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -21451,7 +21451,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -21515,7 +21515,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21579,7 +21579,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -21611,7 +21611,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -21643,7 +21643,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -21771,7 +21771,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -21835,7 +21835,7 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -21899,7 +21899,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -22091,7 +22091,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -22123,7 +22123,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -22251,7 +22251,7 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -22418,7 +22418,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -22450,7 +22450,7 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22642,7 +22642,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -22674,7 +22674,7 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -22706,7 +22706,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -22738,7 +22738,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -22770,7 +22770,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -22802,7 +22802,7 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -22834,7 +22834,7 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -22994,7 +22994,7 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -23026,7 +23026,7 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -23122,7 +23122,7 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -23154,7 +23154,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -23186,7 +23186,7 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -23314,7 +23314,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -23346,7 +23346,7 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -23474,7 +23474,7 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -23538,7 +23538,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23673,7 +23673,7 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -23705,7 +23705,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -23865,7 +23865,7 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -23897,7 +23897,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -23961,7 +23961,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -23993,7 +23993,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -24089,7 +24089,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -24121,7 +24121,7 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -24185,7 +24185,7 @@
         <v>5</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -24217,7 +24217,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -24249,7 +24249,7 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -24281,7 +24281,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -24345,7 +24345,7 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -24377,7 +24377,7 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -24409,7 +24409,7 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -24505,7 +24505,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -24537,7 +24537,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -24569,7 +24569,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -24729,7 +24729,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -24793,7 +24793,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24928,7 +24928,7 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -25056,7 +25056,7 @@
         <v>5</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -25152,7 +25152,7 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -25184,7 +25184,7 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -25248,7 +25248,7 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -25280,7 +25280,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -25344,7 +25344,7 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -25408,7 +25408,7 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -25440,7 +25440,7 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -25472,7 +25472,7 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -25536,7 +25536,7 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -25600,7 +25600,7 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -25632,7 +25632,7 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -25664,7 +25664,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -25760,7 +25760,7 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -25792,7 +25792,7 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -25824,7 +25824,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -26048,7 +26048,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
